--- a/tools/importer/reports/import-supermoney-full.report.xlsx
+++ b/tools/importer/reports/import-supermoney-full.report.xlsx
@@ -70,7 +70,7 @@
     <t>supermoney-full</t>
   </si>
   <si>
-    <t>2026-08-11T12:33:16.992Z</t>
+    <t>2026-08-11T12:56:43.511Z</t>
   </si>
 </sst>
 </file>

--- a/tools/importer/reports/import-supermoney-full.report.xlsx
+++ b/tools/importer/reports/import-supermoney-full.report.xlsx
@@ -70,7 +70,7 @@
     <t>supermoney-full</t>
   </si>
   <si>
-    <t>2026-08-11T12:56:43.511Z</t>
+    <t>2026-08-11T13:13:31.903Z</t>
   </si>
 </sst>
 </file>

--- a/tools/importer/reports/import-supermoney-full.report.xlsx
+++ b/tools/importer/reports/import-supermoney-full.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,78 @@
     <t>url</t>
   </si>
   <si>
+    <t>forex-card.report.json</t>
+  </si>
+  <si>
+    <t>["hero-p"]</t>
+  </si>
+  <si>
+    <t>forex-card</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>2026-08-11T11:18:55.155Z</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.kotak.bank.in/en/personal-banking/cards/prepaid-card/forex-card.html</t>
+  </si>
+  <si>
+    <t>nav.report.json</t>
+  </si>
+  <si>
+    <t>nav</t>
+  </si>
+  <si>
+    <t>nav-fragment</t>
+  </si>
+  <si>
+    <t>2026-08-14T08:46:48.756Z</t>
+  </si>
+  <si>
+    <t>http://localhost:3000/nav</t>
+  </si>
+  <si>
+    <t>nri-home-loan-features.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","hero-carousel","tabs","intro","feature-carousel","cta","faq","related-products"]</t>
+  </si>
+  <si>
+    <t>nri-home-loan-features</t>
+  </si>
+  <si>
+    <t>2026-08-13T09:42:35.001Z</t>
+  </si>
+  <si>
+    <t>NRI Home Loan</t>
+  </si>
+  <si>
+    <t>http://localhost:3000/nri-home-loan-features</t>
+  </si>
+  <si>
+    <t>preview.report.json</t>
+  </si>
+  <si>
+    <t>["hero-carousel","cards"]</t>
+  </si>
+  <si>
+    <t>preview</t>
+  </si>
+  <si>
+    <t>hero-carousel-demo</t>
+  </si>
+  <si>
+    <t>2026-08-13T04:41:33.806Z</t>
+  </si>
+  <si>
+    <t>http://localhost:3000/content/preview</t>
+  </si>
+  <si>
     <t>supermoney-hero.report.json</t>
   </si>
   <si>
@@ -46,9 +118,6 @@
     <t>supermoney-hero</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>2026-08-11T10:35:49.471Z</t>
   </si>
   <si>
@@ -70,7 +139,7 @@
     <t>supermoney-full</t>
   </si>
   <si>
-    <t>2026-08-11T13:13:31.903Z</t>
+    <t>2026-08-19T07:27:51.571Z</t>
   </si>
 </sst>
 </file>
@@ -459,12 +528,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
@@ -526,25 +595,129 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-supermoney-full.report.xlsx
+++ b/tools/importer/reports/import-supermoney-full.report.xlsx
@@ -130,7 +130,7 @@
     <t>credit-cards/811-super-money-credit-card.report.json</t>
   </si>
   <si>
-    <t>["supermoney-header","supermoney-hero","supermoney-footer"]</t>
+    <t>["supermoney-header","supermoney-hero","supermoney-features","supermoney-features","supermoney-features","supermoney-features","supermoney-steps","supermoney-content","supermoney-footer"]</t>
   </si>
   <si>
     <t>credit-cards/811-super-money-credit-card</t>
@@ -139,7 +139,7 @@
     <t>supermoney-full</t>
   </si>
   <si>
-    <t>2026-08-19T07:27:51.571Z</t>
+    <t>2026-08-19T09:09:46.765Z</t>
   </si>
 </sst>
 </file>
